--- a/daybook-generated-files/2.xlsx
+++ b/daybook-generated-files/2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.37.221.58\file\HV\Capital DayBook\11. NOV\XLSX File\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.37.221.58\Shared Files\HV\Capital DayBook\2026\01. JAN\XLSX File\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC7970FE-BA53-42AE-B558-A81E996082FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{66A3EB6D-7A98-4F66-8CD2-03D1496C1D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="11490" xr2:uid="{DA64B63B-96D6-4627-8CB1-2FA8A3478D40}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="11490" xr2:uid="{665C793E-4CAA-472C-B598-6874F99B59BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Suspense Head Report" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="73">
   <si>
     <t>WESTERN RAILWAY</t>
   </si>
   <si>
-    <t>SUSPENSE HEAD   REPORT FROM 1/11/2025 TO 30/11/2025</t>
+    <t>SUSPENSE HEAD   REPORT FROM 1/1/2026 TO 31/1/2026</t>
   </si>
   <si>
     <t>ALLOCATION : 21417804-***</t>
@@ -67,28 +67,28 @@
     <t>UNIQUE_WORK_ID</t>
   </si>
   <si>
-    <t>04-JV</t>
-  </si>
-  <si>
-    <t>081832501801</t>
-  </si>
-  <si>
-    <t>30/11/2025</t>
-  </si>
-  <si>
-    <t>TPI Bill Payment of WR for the month of SEP-2024 having amount 16803.76 for 0818 vide CO6 = 08010425002067</t>
+    <t>01-JV</t>
+  </si>
+  <si>
+    <t>081832502580</t>
+  </si>
+  <si>
+    <t>31/01/2026</t>
+  </si>
+  <si>
+    <t>RITES INSPECTION BILL</t>
   </si>
   <si>
     <t>***</t>
   </si>
   <si>
-    <t>10446.16</t>
+    <t>11742</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>ELECTRICAL</t>
+    <t>SECURITY</t>
   </si>
   <si>
     <t>RKTS01812G</t>
@@ -100,151 +100,142 @@
     <t>Allocation Total</t>
   </si>
   <si>
-    <t>10446</t>
-  </si>
-  <si>
-    <t>ALLOCATION : 21427551-***</t>
+    <t>ALLOCATION : 21516552-***</t>
   </si>
   <si>
     <t>EGA</t>
   </si>
   <si>
-    <t>08180625000075</t>
-  </si>
-  <si>
-    <t>08180625700028</t>
-  </si>
-  <si>
-    <t>27/11/2025</t>
-  </si>
-  <si>
-    <t>SAL FOR NOV-2025 OF B.U. 18003</t>
-  </si>
-  <si>
-    <t>SALARY OF B.U. 0818003 FOR NOV-2025</t>
-  </si>
-  <si>
-    <t>16591</t>
-  </si>
-  <si>
-    <t>GEN. ADMN.</t>
+    <t>08180625000097</t>
+  </si>
+  <si>
+    <t>08180625700035</t>
+  </si>
+  <si>
+    <t>29/01/2026</t>
+  </si>
+  <si>
+    <t>SAL FOR JAN-2026 OF B.U. 18003</t>
+  </si>
+  <si>
+    <t>SALARY OF B.U. 0818003 FOR JAN-2026</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>SnT</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>150442211001</t>
-  </si>
-  <si>
-    <t>ALLOCATION : 21427552-***</t>
-  </si>
-  <si>
-    <t>53100</t>
-  </si>
-  <si>
-    <t>ALLOCATION : 21516503-***</t>
+    <t>150451233001</t>
+  </si>
+  <si>
+    <t>ALLOCATION : 21516603-***</t>
   </si>
   <si>
     <t>X-I</t>
   </si>
   <si>
-    <t>08180125006045</t>
-  </si>
-  <si>
-    <t>08180125701075</t>
-  </si>
-  <si>
-    <t>03/11/2025</t>
-  </si>
-  <si>
-    <t>MANAGER SBI GYMKHANA BR. RAJKOT .</t>
-  </si>
-  <si>
-    <t>For new power connection for new 08 Nos. Railwat Quarters at OKHA</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>EL/84/1/ADV -</t>
-  </si>
-  <si>
-    <t>150451233001</t>
+    <t>08180125008091</t>
+  </si>
+  <si>
+    <t>08180125701384</t>
+  </si>
+  <si>
+    <t>08/01/2026</t>
+  </si>
+  <si>
+    <t>B.L.MANIA-JAMNAGAR</t>
+  </si>
+  <si>
+    <t>RAILWAY DRAINAGE WORK</t>
+  </si>
+  <si>
+    <t>2046758.22</t>
+  </si>
+  <si>
+    <t>ENGINEERING</t>
+  </si>
+  <si>
+    <t>0818WC25000008 - WR/RJT/Civil/2025/0017</t>
+  </si>
+  <si>
+    <t>150451244001</t>
+  </si>
+  <si>
+    <t>2046758</t>
+  </si>
+  <si>
+    <t>ALLOCATION : 21516663-***</t>
+  </si>
+  <si>
+    <t>184208.39</t>
+  </si>
+  <si>
+    <t>184208</t>
+  </si>
+  <si>
+    <t>ALLOCATION : 21516664-***</t>
   </si>
   <si>
     <t>ALLOCATION : 21646403-***</t>
   </si>
   <si>
-    <t>08180125006314</t>
-  </si>
-  <si>
-    <t>08180125701111</t>
-  </si>
-  <si>
-    <t>11/11/2025</t>
-  </si>
-  <si>
-    <t>For new Community Hall new electricity connection at Morbi Railway Colony</t>
-  </si>
-  <si>
-    <t>12000</t>
-  </si>
-  <si>
-    <t>EL/84/1/PGVCL -</t>
-  </si>
-  <si>
-    <t>150464233004</t>
-  </si>
-  <si>
-    <t>SBNS</t>
-  </si>
-  <si>
-    <t>08180425001308</t>
-  </si>
-  <si>
-    <t>08180425700250</t>
-  </si>
-  <si>
-    <t>20/11/2025</t>
-  </si>
-  <si>
-    <t>AARUSH CORPORATION-RAJKOT</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>75101.7</t>
-  </si>
-  <si>
-    <t>STORES</t>
-  </si>
-  <si>
-    <t>87255717200631 -</t>
-  </si>
-  <si>
-    <t>150464233003</t>
-  </si>
-  <si>
-    <t>65579.67</t>
+    <t>081832502460</t>
+  </si>
+  <si>
+    <t>NO.A/01/60 DATED 06/01/2026 As per IRWCMS system not identified more than one UWID. therefore, adjustment is required to set right the booking to avoid misclassification. description of work SUNR CONSTRUCTION OF NEW COMMUMNITY HALL CONSTRUCTION OF NEW TYPE II QUATERS FOR STAFF WR/RJT/CIVIL/2025/0015 B3</t>
+  </si>
+  <si>
+    <t>318312.72</t>
   </si>
   <si>
     <t>150464243004</t>
   </si>
   <si>
-    <t>152681</t>
+    <t>08180125008041</t>
+  </si>
+  <si>
+    <t>08180125701376</t>
+  </si>
+  <si>
+    <t>07/01/2026</t>
+  </si>
+  <si>
+    <t>N.V. INFRA-RAJKOT</t>
+  </si>
+  <si>
+    <t>3rd running bill</t>
+  </si>
+  <si>
+    <t>1591563.56</t>
+  </si>
+  <si>
+    <t>0818WC24000116 - WR/RJT/Civil/2025/0015</t>
+  </si>
+  <si>
+    <t>1591564</t>
+  </si>
+  <si>
+    <t>318313</t>
   </si>
   <si>
     <t>ALLOCATION : 21646463-***</t>
   </si>
   <si>
-    <t>6759.16</t>
-  </si>
-  <si>
-    <t>5902.19</t>
-  </si>
-  <si>
-    <t>12661</t>
+    <t>28648.14</t>
+  </si>
+  <si>
+    <t>143240.72</t>
+  </si>
+  <si>
+    <t>143241</t>
+  </si>
+  <si>
+    <t>28648</t>
   </si>
   <si>
     <t>ALLOCATION : 21646464-***</t>
@@ -645,19 +636,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1227B202-D04E-4602-B873-85D43A0E3CA8}">
-  <dimension ref="A1:L47"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CCE4F94-319C-45E8-85EB-91FDE30019EB}">
+  <dimension ref="A1:L52"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" customWidth="1"/>
     <col min="2" max="3" width="15.5703125" customWidth="1"/>
     <col min="4" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="5" width="94.85546875" customWidth="1"/>
-    <col min="6" max="6" width="62.140625" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
+    <col min="6" max="6" width="33.7109375" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" customWidth="1"/>
+    <col min="10" max="10" width="38.5703125" customWidth="1"/>
     <col min="11" max="11" width="12.42578125" customWidth="1"/>
     <col min="12" max="12" width="16.28515625" customWidth="1"/>
   </cols>
@@ -744,7 +735,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -787,7 +778,7 @@
         <v>25</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>21</v>
@@ -795,7 +786,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -843,42 +834,42 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -886,7 +877,7 @@
         <v>25</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>21</v>
@@ -894,7 +885,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -944,40 +935,40 @@
     </row>
     <row r="18" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
@@ -985,7 +976,7 @@
         <v>25</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>21</v>
@@ -993,7 +984,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1043,40 +1034,40 @@
     </row>
     <row r="24" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="G24" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
@@ -1084,7 +1075,7 @@
         <v>25</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>21</v>
@@ -1092,7 +1083,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1142,406 +1133,468 @@
     </row>
     <row r="30" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="E30" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="F31" s="2" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="2" t="s">
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="331.5" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="H38" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K31" s="2" t="s">
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A41" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+    </row>
+    <row r="42" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="331.5" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K43" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L31" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
+      <c r="L43" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F44" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="G44" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+    </row>
+    <row r="49" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="331.5" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H50" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="I50" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I32" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K32" s="2" t="s">
+      <c r="I51" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K51" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L32" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F33" s="2" t="s">
+      <c r="L51" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F52" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G52" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
+      <c r="H52" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-    </row>
-    <row r="37" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F40" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-    </row>
-    <row r="44" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F47" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>21</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A43:H43"/>
+  <mergeCells count="10">
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A48:H48"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A4:H4"/>
@@ -1549,7 +1602,7 @@
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="0"/>
